--- a/Output Data Tables/AFAT Outputs/Revenue Tables/2022/Revenue_per_RPM_by_Airline_2022.xlsx
+++ b/Output Data Tables/AFAT Outputs/Revenue Tables/2022/Revenue_per_RPM_by_Airline_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>0.1789</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.00059999999999999995</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0.0073000000000000001</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.0061999999999999998</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0.00089999999999999998</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.00040000000000000002</v>
+      </c>
+      <c r="I25" s="0">
+        <v>0.0135</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0">
+        <v>0.048800000000000003</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0.20780000000000001</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.25659999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>0.1573</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.00029999999999999997</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0.0016000000000000001</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.0047000000000000002</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0.00029999999999999997</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.0011999999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>0.012800000000000001</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0">
+        <v>0.011599999999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0.1782</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.18990000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>0.078799999999999995</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.024</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0.0025000000000000001</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.0057000000000000002</v>
+      </c>
+      <c r="I27" s="0">
+        <v>0.016299999999999999</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0">
+        <v>0.0045999999999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0.12839999999999999</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0">
+        <v>0.0061000000000000004</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.0025000000000000001</v>
+      </c>
+      <c r="K28" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0.15740000000000001</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.15809999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>0.16239999999999999</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.00040000000000000002</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>0.0048999999999999998</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.0071000000000000004</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>0.00080000000000000004</v>
       </c>
-      <c r="G25" s="0">
-        <v>0</v>
-      </c>
-      <c r="H25" s="0">
+      <c r="G29" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" s="0">
         <v>0.0011000000000000001</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>0.013100000000000001</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.00020000000000000001</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>0.032399999999999998</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>0.19</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.22239999999999999</v>
       </c>
     </row>
